--- a/forecast_log.xlsx
+++ b/forecast_log.xlsx
@@ -571,17 +571,45 @@
       </c>
     </row>
     <row r="5" ht="34" customHeight="1">
-      <c r="A5" s="4" t="n"/>
-      <c r="B5" s="5" t="n"/>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="6" t="n"/>
-      <c r="E5" s="5" t="n"/>
-      <c r="F5" s="5" t="n"/>
-      <c r="G5" s="4" t="n"/>
+      <c r="A5" s="4" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>2026Q4</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>中性震荡</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>竣工-25.1%且边际恶化；产量代理-15.1%；开工率历史低位；但政策3/3分、出口降幅收窄、价格有涨价函</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>竣工累计同比 / 三家营收同比 / 存货周转天数 / 奔朗营收</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>46418</v>
+      </c>
       <c r="H5" s="5" t="n"/>
       <c r="I5" s="5" t="n"/>
       <c r="J5" s="5" t="n"/>
-      <c r="K5" s="5" t="n"/>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>首期判断。景气分-0.30。耗材明确偏下行(-1.15)；模具数据不足未判断</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="34" customHeight="1">
       <c r="A6" s="4" t="n"/>
